--- a/wp-snippets/plan/site-improvement-plan-20260919.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260919.xlsx
@@ -1346,7 +1346,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>予定版を掲載中（確定後に図へ差し替え）</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>9/13追加のご要望。動画は主催者（NPO法人まちづくりコンソーシアム）のチャンネルのため、掲載に権利上の問題はありません</t>
+          <t>9/13追加のご要望。9/19に第6回（2024年）のドキュメンタリー動画とショート動画も「もっと知る」ページに追加。いずれも主催者のチャンネルのため、掲載に権利上の問題はありません</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>済</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ほかに掲載したい過去大会の動画があればURL</t>
+          <t>ほかに掲載したい過去大会の動画</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2953,10 +2953,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>第7回の定点映像（主催者のYouTube）を掲載します</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
+          <t>主催者のYouTubeにある第6回ドキュメンタリー・ショートムービー・2024年予告編を「もっと知る」に追加（9/19）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3049,7 +3053,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>「手続きは決まり次第お知らせ」と掲載中</t>
+          <t>決めやすいよう「中止時の払い戻し手続き（案）」を作成しました（サイト改善フォルダ・9/19）。□にチェックを入れてお戻しください</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -3080,22 +3084,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>席種ごとの配置が分かる図。いただければ「花火の見え方」を説明に加えられます</t>
+          <t>席種ごとの配置が分かる図（会場マップと一緒で構いません）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断／⑧ 初めて来る人へ</t>
+          <t>⑦ 座席診断／⑧ 来場ガイド</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>配置の情報がないため「指定席で場所取りが不要」を中心に説明</t>
+          <t>配置の情報がないため「指定席で場所取りが不要」を中心に説明中</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -3103,12 +3107,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>予約ボタンの色をサイト全体でそろえるか（座席診断は文字の読みやすさの基準を満たす少し暗い赤、既存ボタンは従来の赤）</t>
+          <t>予約ボタンの色（異論があればお知らせください）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3118,7 +3122,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>座席診断のみ暗めの赤。ほかは従来どおり</t>
+          <t>座席診断は文字の読みやすさの基準を満たす少し暗い赤のまま運用。ほかは従来どおり</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -3126,12 +3130,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>秋川の観光スポット候補（渓谷・紅葉・飲食店）と所要時間、写真</t>
+          <t>秋川の観光スポットの追加候補（あれば）</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3141,7 +3145,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>周辺観光ページの18スポットから選べます</t>
+          <t>周辺観光ページの18スポットをもとに公開済み。追加があれば反映します</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -3269,7 +3273,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
+          <t>中止判断のタイミングと告知ルール、当日の更新担当者</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>販売サイト各社の払い戻し規定との整合も確認が必要です</t>
+          <t>決めやすいよう「開催可否の判断と告知ルール（案）」を作成しました（サイト改善フォルダ・9/19）。前日17時／当日9時判断などの案に□を付けてお戻しください</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>

--- a/wp-snippets/plan/site-improvement-plan-20260919.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260919.xlsx
@@ -2623,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2677,49 +2677,45 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>最優先</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>チケットページの公開（0-2・0-3・0-4・⑥・⑦）</t>
+          <t>「My花火」パートの扱い（意味・掲載してよいか・説明文）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>0-2・0-3・0-4・⑥・⑦</t>
+          <t>⑫ 音楽リスト／③ 楽しみ方</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>9/15に公開しました</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>公開済み</t>
-        </is>
-      </c>
+          <t>確認でき次第、音楽紹介の記事を再公開し、③⑤⑪の曲目・案内文を戻します</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>9/26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>座席診断のおすすめ振り分け（全20通り）。異論があればお知らせください（回答がなければ現状のまま運用します）</t>
+          <t>①トップページ整理：第1段階（並べ替え・お知らせ縮小・席と料金の明記）の確認用ページのご判断と、第2段階に使う素材（昨年の花火・会場の写真／動画、キャッチコピー、今年の見どころ3点）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断</t>
+          <t>① トップ整理</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>初期案で公開中。結果に「※おすすめは目安です」を表示</t>
+          <t>確認用ページ https://machizukuri-con.or.jp/?page_id=4675&amp;preview=true（要ログイン）。素材が無くても第1段階は公開できます</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2727,49 +2723,45 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>9/26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>A席「子ども2,000円」の年齢区分</t>
+          <t>秋川の観光スポット候補（渓谷・紅葉・飲食店）と所要時間、写真　※追加があれば</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断／チケット／来場ガイド</t>
+          <t>② 体験価値・モデルコース</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>販売サイト（アソビュー）の公式表記「大人13歳以上・子ども12歳以下」をサイトに反映（9/19）。膝上無料の上限年齢は未記載のまま</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>販売サイトの表記で確定</t>
-        </is>
-      </c>
+          <t>周辺観光ページの18スポットをもとに公開済み</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>9/26</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>フリーエリア：グループ全員が西多摩在住である必要があるか</t>
+          <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断／来場ガイド</t>
+          <t>③ 飲食・ステージ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「受付でお住まいを確認できる書類（身分証など）の提示をお願いする場合があります」を反映（9/19、販売サイトの表記）。全員か代表者かは未記載</t>
+          <t>第7回の内容を「参考」として掲載中。確定後に差し替えます</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2777,22 +2769,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5名以上の家族・グループへの案内（隣同士になるか）</t>
+          <t>掲載するInstagram投稿の選定、メディア掲載一覧（媒体・日付・リンク）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断／来場ガイド</t>
+          <t>⑤ SNS・メディアまとめ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>「5名以上の場合は席の組み合わせをお問い合わせからご相談ください」を反映（9/19）。お問い合わせが来た場合の回答方針をご検討ください</t>
+          <t>現在のメディア掲載ページの内容で公開済み</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2800,22 +2792,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1人あたりの換算・差額の表示（異論があればお知らせください）</t>
+          <t>当日プログラム（開場・ステージ進行・飲食開始・打上・終了時刻）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>⑦ 座席診断</t>
+          <t>④ タイムスケジュール／⑨ 当日ガイド</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>表示価格の割り算・引き算のみで「〜の計算です」と記載し、現状のまま運用</t>
+          <t>第7回の時間を「予定」として掲載中</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2823,22 +2815,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>写真の説明文（読み上げ用）の言い回し（異論があればお知らせください）</t>
+          <t>会場マップ最新版（座席の配置・トイレ・救護所・飲食・ステージ）、到着推奨時刻</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>0-4 読み上げ・検索への対応</t>
+          <t>⑧ 来場ガイド／⑨ 当日ガイド／⑦ 座席診断</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>席名と写っているものだけで記載し、現状のまま運用（見た目は変わりません）</t>
+          <t>2024年の会場写真を参考として掲載中。配置が分かれば座席診断に「花火の見え方」を加えられます</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2846,22 +2838,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ふるさと納税・寄付協賛の記載に変更が出たときのご連絡</t>
+          <t>帰りのバス時刻表（交通事業者へ確認）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>⑥ チケット入手方法の整理</t>
+          <t>⑧ 来場ガイド／⑨ 当日ガイド</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>現在の各ページの記載どおりに案内中。変更があれば反映します</t>
+          <t>「確定次第お知らせ」と掲載中</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2869,22 +2861,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>10/17</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>旧URLが載っている媒体（チラシ・QRコード・メール等）の確認</t>
+          <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>0-1 旧URLの転送設定</t>
+          <t>⑩ 天候・開催情報</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>転送設定が完了したため、媒体の差し替えは任意です</t>
+          <t>決めやすいよう「開催可否の判断と告知ルール（案）」「中止時の払い戻し手続き（案）」を用意しました（サイト改善フォルダ）。□にチェックを入れてお戻しください</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2892,22 +2884,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>10/24</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>①トップページ整理・第1段階（並べ替え・お知らせ縮小・席と料金の明記）の確認用ページのご確認。あわせて、第2段階に使う素材：昨年の花火・会場の写真／動画、キャッチコピー、今年の見どころ3点</t>
+          <t>会場マップ・タイムスケジュール・バス時刻表の最終版</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>① トップページの情報整理</t>
+          <t>⑨ 当日ガイドPDF</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>確認用ページ https://machizukuri-con.or.jp/?page_id=4675&amp;preview=true（要ログイン）。素材が無くても第1段階は公開できます</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2915,22 +2907,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>今年の音楽リスト：曲目の確定（進行表にパート6・7、曲No.6・8・11・12・15の抜けがあります）、表記の修正案の確認（VIVANT／Zoo／Mrs. GREEN APPLE／LOVE SONG・CHAGE and ASKA／玉置浩二／Always Remember Us This Way）、「My花火パート」の説明文</t>
+          <t>花火師からのメッセージ（数行）、担当し始めた年、今年の見どころのひと言　※いただければ追記</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>⑫ 今年の音楽リスト</t>
+          <t>⑪ 花火師のページ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>9/13時点の進行表どおりに「予定・変更の場合あり」と明記して掲載します</t>
+          <t>公式サイトの公開情報と写真で公開中</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2943,22 +2935,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ほかに掲載したい過去大会の動画</t>
+          <t>席種ごとのおすすめ定義と各席の写真</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>⑬ 過去大会の動画</t>
+          <t>⑦ 座席診断</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>主催者のYouTubeにある第6回ドキュメンタリー・ショートムービー・2024年予告編を「もっと知る」に追加（9/19）</t>
+          <t>初期案で公開中（結果に「※おすすめは目安です」を表示）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>対応済み</t>
+          <t>公開済み</t>
         </is>
       </c>
     </row>
@@ -2970,17 +2962,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>②③⑤⑧⑩⑪⑫⑬の公開</t>
+          <t>ふるさと納税の返礼品ページURL・受付期限、寄付・協賛の特典内容</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>②③⑤⑧⑩⑪⑫⑬</t>
+          <t>⑥ 購入方法の整理</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>9/16に公開しました。公開URL: /akigawa-day/ ／ /enjoy/ ／ /know-more/ ／ /first-visit/ ／ /kaisai-joho/ ／ /hanabishi/ ／ /news/4572/</t>
+          <t>現在の各ページの記載どおりに案内中。変更があればご連絡ください</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2989,350 +2981,12 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>「My花火」パートの扱い（意味・掲載可否・説明文）。確認でき次第、音楽紹介の記事を再公開します</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>⑫ 音楽リスト／③ 楽しみ方</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>9/17から記事を一時非公開（下書きに保持）。③⑤⑪の曲目・リンクも外しています</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>第8回の会場マップ（席・トイレ・飲食・ステージ・救護所の位置）</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>⑧ 初めて来る方へ／⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2024年の会場写真を参考として掲載中</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>10/17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>中止のときの払い戻しの手続き（申し込み方法・受付期間）</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>⑩ 天候・開催情報</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>決めやすいよう「中止時の払い戻し手続き（案）」を作成しました（サイト改善フォルダ・9/19）。□にチェックを入れてお戻しください</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>花火師からのメッセージ（数行）、秋川流域花火大会を担当し始めた年、今年の見どころのひと言</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>⑪ 花火師のページ</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>公式サイトの公開情報と写真（許諾済み）で公開中。いただければ追記します</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>席種ごとの配置が分かる図（会場マップと一緒で構いません）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断／⑧ 来場ガイド</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>配置の情報がないため「指定席で場所取りが不要」を中心に説明中</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>予約ボタンの色（異論があればお知らせください）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>0-3／⑦</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>座席診断は文字の読みやすさの基準を満たす少し暗い赤のまま運用。ほかは従来どおり</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>秋川の観光スポットの追加候補（あれば）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>② 体験価値・モデルコース</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>周辺観光ページの18スポットをもとに公開済み。追加があれば反映します</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>9/26</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>③ 飲食・ステージ</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>未確定分は「予定」表記で先行公開も可能です</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>10/3</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>掲載するInstagram投稿の選定、メディア掲載一覧（媒体・日付・リンク）</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>⑤ SNS・メディアまとめ</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>当日プログラム（開場・ステージ進行・飲食開始・打上・終了時刻）</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>④ タイムスケジュール／⑨ 当日ガイド／⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>サイトの時間は第7回の記録のままです</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>会場マップ最新版（座席・トイレ・救護所・飲食・ステージ）、到着推奨時刻</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>⑧ 初めて来る人へ／⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>帰りのバス時刻表（交通事業者へ確認）</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>⑧ 初めて来る人へ／⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>アクセスページは「確定次第、順次公開します」のままです</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>10/17</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>中止判断のタイミングと告知ルール、当日の更新担当者</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>⑩ 天候・開催情報</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>決めやすいよう「開催可否の判断と告知ルール（案）」を作成しました（サイト改善フォルダ・9/19）。前日17時／当日9時判断などの案に□を付けてお戻しください</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>10/24</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>会場マップ・タイムスケジュール・バス時刻表の最終版</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>S席の追加販売が終わったとき／フリーエリアが完売したときのご連絡</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>ご連絡いただければ、おすすめする席を変更します</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>※ 座席診断のおすすめの振り分け・1人あたりの換算表示・写真の説明文・予約ボタンの色・A席の年齢区分（大人13歳以上／子ども12歳以下）・フリーエリアの在住確認・5名以上の案内は、販売サイトの表記とサイト担当の判断で運用中です。気になる点があればお知らせください。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/wp-snippets/plan/site-improvement-plan-20260919.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260919.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -121,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,6 +135,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,11 +158,11 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,7 +566,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>来場者目線の導線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って、大会当日（11/14）から逆算して並べています。メールマガジンは第2回以降の配信が未定のため、配信の日程には合わせず、準備ができた施策から順に公開します。　【9月17日時点】0-1〜⑦（チケットページの改善5件）、②③⑤⑧⑩の新ページ5件、⑪花火師のページ・⑬過去大会の動画は公開済みです（内容の点検と修正、各ページ末尾の相互リンクも反映済み）。⑫今年の音楽リストは「My花火」パートの確認のため一時非公開にしています。①トップページの情報整理は、素材が届く前にできる第1段階（並べ替え・お知らせの縮小・席と料金の明記）を確認用ページとして制作済みです。残りは ④当日タイムスケジュール（確定待ち）、⑨当日ガイド（④⑧⑩の確定後）です。9/19に、9/12期限の確認事項のうち販売サイトの公式表記で確定できた3件（年齢区分・在住確認・5名以上の案内）をサイトに反映しました。　状況欄の色 … 緑：公開済み／黄：ご判断・ご対応待ち・一時非公開</t>
+          <t>来場者目線の導線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って、大会当日（11/14）から逆算して並べています。メールマガジンは第2回以降の配信が未定のため、配信の日程には合わせず、準備ができた施策から順に公開します。　【9月17日時点】0-1〜⑦（チケットページの改善5件）、②③⑤⑧⑩の新ページ5件、⑪花火師のページ・⑬過去大会の動画は公開済みです（内容の点検と修正、各ページ末尾の相互リンクも反映済み）。⑫今年の音楽リストは「My花火」パートの確認のため一時非公開にしています。①トップページの情報整理は、素材が届く前にできる第1段階（並べ替え・お知らせの縮小・席と料金の明記）を確認用ページとして制作済みです。残りは ④当日タイムスケジュール（確定待ち）、⑨当日ガイド（④⑧⑩の確定後）です。9/19に、9/12期限の確認事項のうち販売サイトの公式表記で確定できた3件（年齢区分・在住確認・5名以上の案内）をサイトに反映しました。　施策名を押すと、そのページが開きます（⑫は要ログインの確認用ページ）。　状況欄の色 … 緑：公開済み／黄：ご判断・ご対応待ち・一時非公開</t>
         </is>
       </c>
     </row>
@@ -646,7 +653,7 @@
           <t>(即時対応)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>「ページが見つかりません」と表示される旧URLを、お問い合わせページへ転送する</t>
         </is>
@@ -671,7 +678,7 @@
           <t>「ページが見つかりません」の発生 0件</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -696,7 +703,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -718,7 +725,7 @@
           <t>(即時対応)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>チケットページの写真をタップで拡大できるようにする</t>
         </is>
@@ -743,7 +750,7 @@
           <t>押しても反応しない箇所へのタップ 16.7%→10%以下、すぐ前のページに戻る割合 27%→20%以下</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -768,7 +775,7 @@
           <t>（配信する場合）9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -790,7 +797,7 @@
           <t>(即時対応)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>SS席・S席・A席の紹介欄に予約ボタンを追加</t>
         </is>
@@ -815,7 +822,7 @@
           <t>席の紹介欄からの予約クリック数</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -840,7 +847,7 @@
           <t>（配信する場合）9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -862,7 +869,7 @@
           <t>(即時対応)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>読み上げ・検索への対応（写真の説明文、販売サイト対応表の記号を文字に）</t>
         </is>
@@ -887,7 +894,7 @@
           <t>―（見た目は変わりません）</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -912,7 +919,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -934,7 +941,7 @@
           <t>チケットを選ぶ・購入する</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>チケット入手方法の整理「あなたに合った購入方法」</t>
         </is>
@@ -959,7 +966,7 @@
           <t>チケットページ→予約クリック率、ふるさと納税・寄付ページへの遷移数</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -984,7 +991,7 @@
           <t>（配信する場合）9/17 第2回配信</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1006,7 +1013,7 @@
           <t>自分に合った楽しみ方を見つける</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>座席診断（どなたと観覧？→何を重視？→おすすめの席→予約ボタン）</t>
         </is>
@@ -1031,7 +1038,7 @@
           <t>診断の開始数・結果表示数、診断→予約クリック率、席種別の販売バランス</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1056,7 +1063,7 @@
           <t>（配信する場合）9/17 第2回配信「座席写真で席選び」と連動</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1078,7 +1085,7 @@
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>トップページの情報整理（写真・動画→コンセプト→今年の見どころ→チケット導線）</t>
         </is>
@@ -1103,7 +1110,7 @@
           <t>トップページを下まで読んだ割合（現状51%）、トップ→チケットページ遷移率</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1128,7 +1135,7 @@
           <t>（配信する場合）10/8 第3回配信前</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>第1段階の案を制作済み（内容のご確認待ち）</t>
         </is>
@@ -1150,7 +1157,7 @@
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>「東京から約60分、紅葉・秋川渓谷・花火の秋の日帰り旅」の体験価値と「秋川で一日過ごすモデルコース」</t>
         </is>
@@ -1175,7 +1182,7 @@
           <t>該当箇所の閲覧数、「秋川 紅葉」「サマーランド 花火」等の検索表示回数とクリック率、滞在時間</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1200,7 +1207,7 @@
           <t>（配信する場合）10/8 第3回配信「体験価値」に本文リンク</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1222,7 +1229,7 @@
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>飲食・ステージのアピール（食べる／見る／楽しむ／感動する）</t>
         </is>
@@ -1247,7 +1254,7 @@
           <t>該当箇所の閲覧数、出店者募集ページとの回遊</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1272,7 +1279,7 @@
           <t>（配信する場合）10/8 第3回配信</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1294,7 +1301,7 @@
           <t>行きたくなる</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>当日タイムスケジュールの掲載</t>
         </is>
@@ -1319,7 +1326,7 @@
           <t>閲覧数、当日ガイドへの流入</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>中（確定後は高）</t>
         </is>
@@ -1344,7 +1351,7 @@
           <t>（配信する場合）10/22 第4回配信</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>予定版を掲載中（確定後に図へ差し替え）</t>
         </is>
@@ -1366,7 +1373,7 @@
           <t>知る</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SNS・メディア出演情報のまとめ「秋川流域花火大会をもっと知る」</t>
         </is>
@@ -1391,7 +1398,7 @@
           <t>ページ閲覧数、SNSへのクリック数</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
@@ -1416,7 +1423,7 @@
           <t>（配信する場合）10/22 第4回配信</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1438,7 +1445,7 @@
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>「初めて来る人へ」ページ（行く前／会場内／帰り）</t>
         </is>
@@ -1463,7 +1470,7 @@
           <t>ページ閲覧数、よくある質問・交通アクセスとの回遊、お問い合わせ件数の減少</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1488,7 +1495,7 @@
           <t>（配信する場合）10/22 第4回配信「購入前確認」に本文リンク</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1510,7 +1517,7 @@
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>天候・開催情報（開催・中止の判断、雨天対応、服装・防寒、当日の天気）</t>
         </is>
@@ -1535,7 +1542,7 @@
           <t>当日週のトップページ閲覧数、開催情報ページ閲覧数、お問い合わせ件数</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1560,7 +1567,7 @@
           <t>11/13〜14 当日運用（配信する場合は10/31 第5回配信）</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1607,7 +1614,7 @@
           <t>ダウンロード数（現状は週6件）</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1632,7 +1639,7 @@
           <t>大会前週に案内（配信する場合は10/31 第5回配信に添付）</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1654,7 +1661,7 @@
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>花火師のページ（株式会社ホソヤエンタープライズ＝あきる野市の花火師）</t>
         </is>
@@ -1679,7 +1686,7 @@
           <t>ページの閲覧数、ページからチケットページへ進んだ数</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1704,7 +1711,7 @@
           <t>SNSで告知（配信する場合はその本文からもリンク）</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1726,7 +1733,7 @@
           <t>行きたくなる</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>今年（第8回）の音楽リストの掲載（お知らせ記事＋③「楽しみ方」の音楽欄）</t>
         </is>
@@ -1751,7 +1758,7 @@
           <t>お知らせ記事の閲覧数、記事からチケットページへ進んだ数</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1776,7 +1783,7 @@
           <t>SNSで告知（配信する場合はその本文からもリンク）</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>一時非公開（内容確認中）</t>
         </is>
@@ -1798,7 +1805,7 @@
           <t>知る</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>過去大会の動画（第7回 定点映像・YouTube）の掲載</t>
         </is>
@@ -1823,7 +1830,7 @@
           <t>動画の再生数（YouTube）、掲載ページの閲覧数</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1848,7 +1855,7 @@
           <t>SNSで告知</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>公開済み（9/16）</t>
         </is>
@@ -1895,7 +1902,7 @@
           <t>配信からの訪問数・予約クリック数が正確に分かる</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1920,7 +1927,7 @@
           <t>配信する場合の全配信</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>配信が決まった場合に実施</t>
         </is>
@@ -1935,6 +1942,24 @@
   <mergeCells count="1">
     <mergeCell ref="A2:N2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1963,7 +1988,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>週別スケジュール（✔公開=公開済み　■=作業　★=公開予定　◆=節目）　※2026年9月19日時点</t>
         </is>
@@ -2042,32 +2067,32 @@
           <t>節目（大会当日。メールマガジンの配信は未定）</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>9/17（配信する場合）</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>10/8（配信する場合）</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr"/>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>10/22（配信する場合）</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>10/31 販売最終（配信する場合）</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>11/14 大会当日</t>
         </is>
@@ -2079,25 +2104,25 @@
           <t>0-1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>旧URLの転送設定</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2105,25 +2130,25 @@
           <t>0-2</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>写真をタップで拡大</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2131,25 +2156,25 @@
           <t>0-3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>席ごとの予約ボタン</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2157,25 +2182,25 @@
           <t>0-4</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>読み上げ・検索への対応</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2183,25 +2208,25 @@
           <t>⑥</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>チケット入手方法の整理</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2209,25 +2234,25 @@
           <t>⑦</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>座席診断</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2235,33 +2260,33 @@
           <t>①</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>トップページの情報整理</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>素材待ち</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2269,29 +2294,29 @@
           <t>②</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>体験価値・モデルコース</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2299,29 +2324,29 @@
           <t>③</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>飲食・ステージのアピール</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2329,29 +2354,29 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>SNS・メディアまとめ</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2359,29 +2384,29 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>当日タイムスケジュール</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>確定待ち</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2389,29 +2414,29 @@
           <t>⑧</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>初めて来る人へ</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2419,33 +2444,33 @@
           <t>⑩</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>天候・開催情報</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
@@ -2462,24 +2487,24 @@
           <t>当日ガイド</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr"/>
+      <c r="L18" s="15" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
@@ -2491,29 +2516,29 @@
           <t>⑪</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>花火師のページ</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2521,25 +2546,25 @@
           <t>⑫</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>今年の音楽リスト</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>一時非公開</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2547,25 +2572,25 @@
           <t>⑬</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>過去大会の動画</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>✔公開</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2578,41 +2603,59 @@
           <t>配信リンクの計測設定（配信する場合のみ）</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>配信時</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>配信時</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>配信時</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>配信時</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>※「✔公開」は公開済み（9/16時点）。★は当初の公開目標日で、前倒しで公開できたものはそのまま残しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2634,7 +2677,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>実行委員会でご用意・ご判断いただきたいこと（期限順）　※2026年9月19日更新</t>
         </is>
@@ -2982,7 +3025,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>※ 座席診断のおすすめの振り分け・1人あたりの換算表示・写真の説明文・予約ボタンの色・A席の年齢区分（大人13歳以上／子ども12歳以下）・フリーエリアの在住確認・5名以上の案内は、販売サイトの表記とサイト担当の判断で運用中です。気になる点があればお知らせください。</t>
         </is>
@@ -3013,7 +3056,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>効果を測る指標　現状値（2026年8月29日〜9月4日）と目標</t>
         </is>
@@ -3371,7 +3414,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>【新】座席診断を始めた数（週）</t>
         </is>
@@ -3398,7 +3441,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>【新】診断結果まで進んだ数（週）</t>
         </is>
@@ -3425,7 +3468,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>【新】診断結果から予約ボタンを押した割合</t>
         </is>
@@ -3452,7 +3495,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>【新】診断でおすすめされた席の内訳</t>
         </is>
@@ -3479,7 +3522,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>【新】写真の拡大表示の利用</t>
         </is>
@@ -3506,7 +3549,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>【新】花火師ページの閲覧数と、チケットページへ進んだ数（週）</t>
         </is>
@@ -3533,7 +3576,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>【新】音楽リストのお知らせの閲覧数（週）</t>
         </is>
@@ -3560,7 +3603,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>【新】第7回 定点映像の再生数</t>
         </is>

--- a/wp-snippets/plan/site-improvement-plan-20260919.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260919.xlsx
@@ -3045,7 +3045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3058,7 +3058,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>効果を測る指標　現状値（2026年8月29日〜9月4日）と目標</t>
+          <t>効果を測る指標　現状値（2026年9月12日〜9月18日）と目標　※（ ）内は前の週 9/5〜9/11。計測日 9/19</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1,340人 / 3,930回（前週比 +101% / +110%）</t>
+          <t>1,030人 / 3,140回（サイト内集計）　アクセス解析では 823人・1,055回の訪問（前の週 713人・958回）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>サイト内のアクセス集計</t>
+          <t>サイト内のアクセス集計・アクセス解析</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>648回 / 14.4% / 5.6位</t>
+          <t>533回 / 17.3% / 5.4位（8/29〜9/4は 648回 / 14.4% / 5.6位）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3146,17 +3146,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>チケットページの閲覧数（28日間）</t>
+          <t>チケットページの閲覧数（週）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2,171回</t>
+          <t>609回・375人（サイト全体の25%）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3,000回</t>
+          <t>―（28日間で3,000回）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>316回（前週比 +185%）</t>
+          <t>アソビュー216回（前の週203回）、ぴあ49（40）、楽天35（34）、JRE MALL 8、KKday 6、さとふる22（23）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>―（行動分析ツールのサインインが切れており未取得）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>27%（411件）</t>
+          <t>―（同上）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>16.7%（253件）</t>
+          <t>―（同上）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>86%（新規711人／823人）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>行動分析ツール</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>11件（正確に計測できていない状態）</t>
+          <t>―（配信なし）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>21件（15人）</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>行動分析ツール</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>旧URLの転送設定が完了（9/13）</t>
+          <t>0件（旧URLの転送設定が有効）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3389,12 +3389,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>チケット販売（累計・9月4日時点）</t>
+          <t>チケット販売（累計・9月19日時点）</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>882席 / 5,518,000円（目標比 20.5%）</t>
+          <t>1,140席 / 6,661,000円（目標比 24.8%）</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>未計測（公開後に取得）</t>
+          <t>52回・41人（公開9/15からの4日間）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>未計測</t>
+          <t>63回・38人（始めた人の93%が結果まで到達）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>未計測</t>
+          <t>5回 / 38人 = 13%</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>未計測</t>
+          <t>未集計（計測項目を9/16に登録。次回から取得）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>未計測</t>
+          <t>―（行動分析ツールの未取得のため次回）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3551,12 +3551,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>【新】花火師ページの閲覧数と、チケットページへ進んだ数（週）</t>
+          <t>【新】新ページの閲覧数（公開9/16〜9/18の3日間）</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>未計測（公開後に取得）</t>
+          <t>来場ガイド14回（平均2分2秒）、楽しみ方5回、音楽紹介5回。ほかは3回以下（トップページの入口は9/17〜、メニューは9/19に追加）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3571,59 +3571,32 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>⑪</t>
+          <t>②③⑤⑧⑩⑪</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>【新】音楽リストのお知らせの閲覧数（週）</t>
+          <t>【新】第7回 定点映像の再生数</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>未計測（公開後に取得）</t>
+          <t>69回（YouTube累計・9/19時点）、第6回ドキュメンタリー 418回</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>公開週のお知らせの中で最多</t>
+          <t>公開後2週間の実測をもとに設定</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>アクセス解析</t>
+          <t>YouTubeの管理画面</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>⑫</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>【新】第7回 定点映像の再生数</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>未計測（公開後に取得）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>公開後2週間の実測をもとに設定</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>YouTubeの管理画面</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>⑬</t>
         </is>
